--- a/samples/2_devices_invalid.xlsx
+++ b/samples/2_devices_invalid.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,6 +436,8 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,6 +519,16 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>management_ip6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>primary address v4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>primary address v6</t>
         </is>
       </c>
     </row>
@@ -577,6 +589,12 @@
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>192.0.2.30/24</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -635,6 +653,8 @@
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -693,6 +713,8 @@
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -751,6 +773,8 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -809,6 +833,8 @@
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -867,6 +893,8 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -925,6 +953,8 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -983,6 +1013,8 @@
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1041,6 +1073,8 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1099,6 +1133,8 @@
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1153,6 +1189,12 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>192.0.2.51/24</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1211,6 +1253,8 @@
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1269,6 +1313,8 @@
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1327,6 +1373,8 @@
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1385,6 +1433,8 @@
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
